--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>61.28677</v>
+      </c>
+      <c r="C2">
+        <v>94.79584</v>
+      </c>
+      <c r="D2">
+        <v>80.76833000000001</v>
+      </c>
+      <c r="E2">
+        <v>46.88501</v>
+      </c>
+      <c r="F2">
         <v>61.62378</v>
       </c>
-      <c r="C2">
-        <v>61.28677</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>99.67523</v>
       </c>
-      <c r="E2">
-        <v>94.79584</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>101.5367</v>
       </c>
-      <c r="G2">
-        <v>80.76833000000001</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>68.77522999999999</v>
-      </c>
-      <c r="I2">
-        <v>46.88501</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>62.57726</v>
+      </c>
+      <c r="C3">
+        <v>95.31820999999999</v>
+      </c>
+      <c r="D3">
+        <v>79.89409999999999</v>
+      </c>
+      <c r="E3">
+        <v>43.08568</v>
+      </c>
+      <c r="F3">
         <v>62.77784</v>
       </c>
-      <c r="C3">
-        <v>62.57726</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>100.137</v>
       </c>
-      <c r="E3">
-        <v>95.31820999999999</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>104.1166</v>
       </c>
-      <c r="G3">
-        <v>79.89409999999999</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>62.79803</v>
-      </c>
-      <c r="I3">
-        <v>43.08568</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>61.8123</v>
+      </c>
+      <c r="C4">
+        <v>97.42161</v>
+      </c>
+      <c r="D4">
+        <v>84.68208</v>
+      </c>
+      <c r="E4">
+        <v>41.38211</v>
+      </c>
+      <c r="F4">
         <v>62.02805</v>
       </c>
-      <c r="C4">
-        <v>61.8123</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>103.0662</v>
       </c>
-      <c r="E4">
-        <v>97.42161</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>103.4682</v>
       </c>
-      <c r="G4">
-        <v>84.68208</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>53.98374</v>
-      </c>
-      <c r="I4">
-        <v>41.38211</v>
       </c>
     </row>
     <row r="5">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>57.93269</v>
+      </c>
+      <c r="C5">
+        <v>95.75114000000001</v>
+      </c>
+      <c r="D5">
+        <v>74.70356</v>
+      </c>
+      <c r="E5">
+        <v>19.54023</v>
+      </c>
+      <c r="F5">
         <v>58.41346</v>
       </c>
-      <c r="C5">
-        <v>57.93269</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>102.5797</v>
       </c>
-      <c r="E5">
-        <v>95.75114000000001</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>98.41898</v>
       </c>
-      <c r="G5">
-        <v>74.70356</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>27.35632</v>
-      </c>
-      <c r="I5">
-        <v>19.54023</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>68.05970000000001</v>
+      </c>
+      <c r="C6">
+        <v>92.74047</v>
+      </c>
+      <c r="D6">
+        <v>83.20895</v>
+      </c>
+      <c r="E6">
+        <v>32.4165</v>
+      </c>
+      <c r="F6">
         <v>68.95522</v>
       </c>
-      <c r="C6">
-        <v>68.05970000000001</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>97.82214</v>
       </c>
-      <c r="E6">
-        <v>92.74047</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>116.4179</v>
       </c>
-      <c r="G6">
-        <v>83.20895</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>41.25737</v>
-      </c>
-      <c r="I6">
-        <v>32.4165</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>64.07244</v>
+      </c>
+      <c r="C7">
+        <v>97.00397</v>
+      </c>
+      <c r="D7">
+        <v>75.20612</v>
+      </c>
+      <c r="E7">
+        <v>32.9559</v>
+      </c>
+      <c r="F7">
         <v>64.17034</v>
       </c>
-      <c r="C7">
-        <v>64.07244</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>108.3766</v>
       </c>
-      <c r="E7">
-        <v>97.00397</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>120.4358</v>
       </c>
-      <c r="G7">
-        <v>75.20612</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>44.36829</v>
-      </c>
-      <c r="I7">
-        <v>32.9559</v>
       </c>
     </row>
     <row r="8">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>67.35536999999999</v>
+      </c>
+      <c r="C8">
+        <v>96.45528</v>
+      </c>
+      <c r="D8">
+        <v>83.34995000000001</v>
+      </c>
+      <c r="E8">
+        <v>33.97186</v>
+      </c>
+      <c r="F8">
         <v>67.56198000000001</v>
       </c>
-      <c r="C8">
-        <v>67.35536999999999</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>102.2431</v>
       </c>
-      <c r="E8">
-        <v>96.45528</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>103.988</v>
       </c>
-      <c r="G8">
-        <v>83.34995000000001</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>47.08171</v>
-      </c>
-      <c r="I8">
-        <v>33.97186</v>
       </c>
     </row>
     <row r="9">
@@ -628,25 +628,25 @@
         <v>53.76344</v>
       </c>
       <c r="C9">
+        <v>96.23477</v>
+      </c>
+      <c r="D9">
+        <v>91.23932000000001</v>
+      </c>
+      <c r="E9">
+        <v>33.75</v>
+      </c>
+      <c r="F9">
         <v>53.76344</v>
       </c>
-      <c r="D9">
+      <c r="G9">
         <v>100</v>
       </c>
-      <c r="E9">
-        <v>96.23477</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>106.8376</v>
       </c>
-      <c r="G9">
-        <v>91.23932000000001</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>43.625</v>
-      </c>
-      <c r="I9">
-        <v>33.75</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>60.96544</v>
+      </c>
+      <c r="C10">
+        <v>95.26029</v>
+      </c>
+      <c r="D10">
+        <v>81.60642</v>
+      </c>
+      <c r="E10">
+        <v>30.28313</v>
+      </c>
+      <c r="F10">
         <v>61.26341</v>
       </c>
-      <c r="C10">
-        <v>60.96544</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>99.8446</v>
       </c>
-      <c r="E10">
-        <v>95.26029</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>99.83936</v>
       </c>
-      <c r="G10">
-        <v>81.60642</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>42.34715</v>
-      </c>
-      <c r="I10">
-        <v>30.28313</v>
       </c>
     </row>
     <row r="11">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>62.9648</v>
+      </c>
+      <c r="C11">
+        <v>95.65355</v>
+      </c>
+      <c r="D11">
+        <v>85.83743</v>
+      </c>
+      <c r="E11">
+        <v>35.72419</v>
+      </c>
+      <c r="F11">
         <v>63.01438</v>
       </c>
-      <c r="C11">
-        <v>62.9648</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>99.71653999999999</v>
       </c>
-      <c r="E11">
-        <v>95.65355</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>103.633</v>
       </c>
-      <c r="G11">
-        <v>85.83743</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>50</v>
-      </c>
-      <c r="I11">
-        <v>35.72419</v>
       </c>
     </row>
     <row r="12">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>62.27642</v>
+      </c>
+      <c r="C12">
+        <v>96.96711999999999</v>
+      </c>
+      <c r="D12">
+        <v>83.00211</v>
+      </c>
+      <c r="E12">
+        <v>36.01063</v>
+      </c>
+      <c r="F12">
         <v>62.38095</v>
       </c>
-      <c r="C12">
-        <v>62.27642</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>101.2998</v>
       </c>
-      <c r="E12">
-        <v>96.96711999999999</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>102.2734</v>
       </c>
-      <c r="G12">
-        <v>83.00211</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>48.59755</v>
-      </c>
-      <c r="I12">
-        <v>36.01063</v>
       </c>
     </row>
     <row r="13">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>57.91246</v>
+      </c>
+      <c r="C13">
+        <v>96.78570999999999</v>
+      </c>
+      <c r="D13">
+        <v>87.05722</v>
+      </c>
+      <c r="E13">
+        <v>40.17216</v>
+      </c>
+      <c r="F13">
         <v>58.02469</v>
       </c>
-      <c r="C13">
-        <v>57.91246</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>100.6429</v>
       </c>
-      <c r="E13">
-        <v>96.78570999999999</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>102.5886</v>
       </c>
-      <c r="G13">
-        <v>87.05722</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>52.94118</v>
-      </c>
-      <c r="I13">
-        <v>40.17216</v>
       </c>
     </row>
     <row r="14">
@@ -780,28 +780,28 @@
         </is>
       </c>
       <c r="B14">
+        <v>57.2284</v>
+      </c>
+      <c r="C14">
+        <v>97.44112</v>
+      </c>
+      <c r="D14">
+        <v>80.44992000000001</v>
+      </c>
+      <c r="E14">
+        <v>28.24705</v>
+      </c>
+      <c r="F14">
         <v>57.5278</v>
       </c>
-      <c r="C14">
-        <v>57.2284</v>
-      </c>
-      <c r="D14">
+      <c r="G14">
         <v>104.9724</v>
       </c>
-      <c r="E14">
-        <v>97.44112</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>95.34012</v>
       </c>
-      <c r="G14">
-        <v>80.44992000000001</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>35.604</v>
-      </c>
-      <c r="I14">
-        <v>28.24705</v>
       </c>
     </row>
     <row r="15">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="B15">
+        <v>56.53129</v>
+      </c>
+      <c r="C15">
+        <v>96.32893</v>
+      </c>
+      <c r="D15">
+        <v>84.81376</v>
+      </c>
+      <c r="E15">
+        <v>34.98452</v>
+      </c>
+      <c r="F15">
         <v>56.75082</v>
       </c>
-      <c r="C15">
-        <v>56.53129</v>
-      </c>
-      <c r="D15">
+      <c r="G15">
         <v>100.3671</v>
       </c>
-      <c r="E15">
-        <v>96.32893</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>97.70773</v>
       </c>
-      <c r="G15">
-        <v>84.81376</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>45.27864</v>
-      </c>
-      <c r="I15">
-        <v>34.98452</v>
       </c>
     </row>
     <row r="16">
@@ -845,25 +845,25 @@
         <v>50.57915</v>
       </c>
       <c r="C16">
+        <v>97.97297</v>
+      </c>
+      <c r="D16">
+        <v>87.3913</v>
+      </c>
+      <c r="E16">
+        <v>37.88546</v>
+      </c>
+      <c r="F16">
         <v>50.57915</v>
       </c>
-      <c r="D16">
+      <c r="G16">
         <v>103.3784</v>
       </c>
-      <c r="E16">
-        <v>97.97297</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>102.1739</v>
       </c>
-      <c r="G16">
-        <v>87.3913</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>46.69603</v>
-      </c>
-      <c r="I16">
-        <v>37.88546</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:36</t>
+    <t xml:space="preserve">2026-08-02 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:38</t>
+    <t xml:space="preserve">2026-08-05 10:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:30</t>
+    <t xml:space="preserve">2026-08-05 18:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 18:11</t>
+    <t xml:space="preserve">2026-08-16 09:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:43</t>
+    <t xml:space="preserve">2026-08-19 11:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:37</t>
+    <t xml:space="preserve">2026-08-28 11:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:19</t>
+    <t xml:space="preserve">2026-09-06 17:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
